--- a/GBL-24136-Geotech-Report-MA .xlsx
+++ b/GBL-24136-Geotech-Report-MA .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/rigid-inclusions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D3FA57-9922-AC4C-88B2-BF5454B944A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82ED602E-FBCB-4C46-902F-9E5EFBDC7E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54500" yWindow="620" windowWidth="30340" windowHeight="19720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="54500" yWindow="620" windowWidth="30340" windowHeight="19720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Project &amp; BH Summary" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="6. TRT Results" sheetId="6" r:id="rId6"/>
     <sheet name="7. Chemical Analysis" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -2169,14 +2169,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2185,17 +2182,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2520,7 +2520,7 @@
       <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="13"/>
@@ -2529,136 +2529,136 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="20"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="20"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="20"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="20"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="13"/>
@@ -2678,7 +2678,7 @@
       <c r="F17" s="13"/>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="13"/>
@@ -2694,12 +2694,12 @@
       <c r="B20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
@@ -2708,12 +2708,12 @@
       <c r="B21" s="4">
         <v>20</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="20"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
@@ -2722,12 +2722,12 @@
       <c r="B22" s="4">
         <v>4</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
@@ -2736,12 +2736,12 @@
       <c r="B23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
@@ -2750,12 +2750,12 @@
       <c r="B24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
@@ -2764,12 +2764,12 @@
       <c r="B25" s="4">
         <v>0.9</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
@@ -2778,15 +2778,15 @@
       <c r="B26" s="4">
         <v>2.4</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="13"/>
@@ -2956,7 +2956,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B38" s="13"/>
@@ -2969,23 +2969,23 @@
       <c r="A39" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="20"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="19"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="20"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="19"/>
       <c r="F40" s="4" t="s">
         <v>65</v>
       </c>
@@ -2994,12 +2994,12 @@
       <c r="A41" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="20"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="19"/>
       <c r="F41" s="4" t="s">
         <v>68</v>
       </c>
@@ -3008,12 +3008,12 @@
       <c r="A42" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="20"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="19"/>
       <c r="F42" s="4" t="s">
         <v>71</v>
       </c>
@@ -3022,18 +3022,32 @@
       <c r="A43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="20"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="4" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C21:F21"/>
@@ -3050,20 +3064,6 @@
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3092,7 +3092,7 @@
       <c r="H1" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>76</v>
       </c>
       <c r="B3" s="13"/>
@@ -3219,7 +3219,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>91</v>
       </c>
       <c r="B11" s="13"/>
@@ -3231,23 +3231,23 @@
       <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="23" t="s">
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="3" t="s">
         <v>95</v>
       </c>
@@ -3427,7 +3427,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>116</v>
       </c>
       <c r="B22" s="13"/>
@@ -3499,7 +3499,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>129</v>
       </c>
       <c r="B28" s="13"/>
@@ -3514,88 +3514,88 @@
       <c r="A29" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="20"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="19"/>
+    </row>
+    <row r="30" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="20"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" spans="1:8" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="20"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="19"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="20"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="19"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="20"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="19"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="20"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="16" t="s">
         <v>142</v>
       </c>
       <c r="B36" s="13"/>
@@ -3610,116 +3610,116 @@
       <c r="A37" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="20"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="19"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="20"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="19"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="20"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="19"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="20"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="19"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="20"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="19"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="20"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="19"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="20"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="19"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="20"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="19"/>
     </row>
     <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="16" t="s">
         <v>153</v>
       </c>
       <c r="B46" s="13"/>
@@ -3731,203 +3731,239 @@
       <c r="H46" s="13"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="18">
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="17">
         <v>0.33</v>
       </c>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="20"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="19"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="18">
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="17">
         <v>3</v>
       </c>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="20"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="19"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="18">
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="17">
         <v>0.5</v>
       </c>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="20"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="19"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="18" t="s">
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="20"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="19"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="18" t="s">
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="20"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="19"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="18" t="s">
+      <c r="A52" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="18" t="s">
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="20"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="19"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="18" t="s">
+      <c r="A53" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="18" t="s">
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="20"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="19"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="18" t="s">
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="20"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="19"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="18" t="s">
+      <c r="A55" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="18" t="s">
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="20"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="19"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="18" t="s">
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="20"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="19"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="18" t="s">
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="20"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="19"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="18" t="s">
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="20"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="19"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="18" t="s">
+      <c r="A59" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="18" t="s">
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="20"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="19"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="18" t="s">
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="20"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E59:H59"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="B31:H31"/>
     <mergeCell ref="E52:H52"/>
@@ -3944,42 +3980,6 @@
     <mergeCell ref="E60:H60"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="B44:H44"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6702,7 +6702,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A94" s="17" t="s">
+      <c r="A94" s="14" t="s">
         <v>311</v>
       </c>
       <c r="B94" s="13"/>
@@ -6828,7 +6828,7 @@
       <c r="M1" s="13"/>
     </row>
     <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>318</v>
       </c>
       <c r="B3" s="13"/>
@@ -7049,7 +7049,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="42" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>346</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="42" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>358</v>
       </c>
@@ -7337,7 +7337,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>361</v>
       </c>
       <c r="B18" s="13"/>
@@ -7810,7 +7810,7 @@
       </c>
     </row>
     <row r="33" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>373</v>
       </c>
       <c r="B33" s="13"/>
@@ -7950,7 +7950,7 @@
       </c>
     </row>
     <row r="38" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="25" t="s">
         <v>389</v>
       </c>
       <c r="B38" s="13"/>
@@ -7967,7 +7967,7 @@
       <c r="M38" s="13"/>
     </row>
     <row r="40" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="16" t="s">
         <v>390</v>
       </c>
       <c r="B40" s="13"/>
@@ -8054,7 +8054,7 @@
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="24" t="s">
         <v>403</v>
       </c>
       <c r="B48" s="13"/>
@@ -8557,7 +8557,7 @@
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="24" t="s">
         <v>459</v>
       </c>
       <c r="B73" s="13"/>
@@ -9071,7 +9071,7 @@
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="24" t="s">
         <v>461</v>
       </c>
       <c r="B99" s="13"/>
@@ -9887,7 +9887,7 @@
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A148" s="16" t="s">
+      <c r="A148" s="24" t="s">
         <v>516</v>
       </c>
       <c r="B148" s="13"/>
@@ -10703,7 +10703,7 @@
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A196" s="17" t="s">
+      <c r="A196" s="14" t="s">
         <v>517</v>
       </c>
       <c r="B196" s="13"/>
@@ -10720,7 +10720,7 @@
       <c r="M196" s="13"/>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A197" s="14" t="s">
+      <c r="A197" s="25" t="s">
         <v>518</v>
       </c>
       <c r="B197" s="13"/>
@@ -10737,7 +10737,7 @@
       <c r="M197" s="13"/>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A198" s="14" t="s">
+      <c r="A198" s="25" t="s">
         <v>519</v>
       </c>
       <c r="B198" s="13"/>
@@ -10754,7 +10754,7 @@
       <c r="M198" s="13"/>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A199" s="14" t="s">
+      <c r="A199" s="25" t="s">
         <v>520</v>
       </c>
       <c r="B199" s="13"/>
@@ -10771,7 +10771,7 @@
       <c r="M199" s="13"/>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A200" s="14" t="s">
+      <c r="A200" s="25" t="s">
         <v>521</v>
       </c>
       <c r="B200" s="13"/>
@@ -10788,7 +10788,7 @@
       <c r="M200" s="13"/>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A201" s="14" t="s">
+      <c r="A201" s="25" t="s">
         <v>522</v>
       </c>
       <c r="B201" s="13"/>
@@ -10805,7 +10805,7 @@
       <c r="M201" s="13"/>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A202" s="14" t="s">
+      <c r="A202" s="25" t="s">
         <v>523</v>
       </c>
       <c r="B202" s="13"/>
@@ -10823,6 +10823,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A199:M199"/>
     <mergeCell ref="A73:M73"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A197:M197"/>
@@ -10839,7 +10840,6 @@
     <mergeCell ref="A38:M38"/>
     <mergeCell ref="A33:M33"/>
     <mergeCell ref="A99:M99"/>
-    <mergeCell ref="A199:M199"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -10873,7 +10873,7 @@
       <c r="I1" s="13"/>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>525</v>
       </c>
       <c r="B3" s="13"/>
@@ -10901,12 +10901,12 @@
       <c r="E4" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="21" t="s">
         <v>529</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="20"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
@@ -10924,12 +10924,12 @@
       <c r="E5" s="4">
         <v>0.15</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="20"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
@@ -10947,12 +10947,12 @@
       <c r="E6" s="4">
         <v>0.15</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="20"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
@@ -10970,12 +10970,12 @@
       <c r="E7" s="4">
         <v>0.23</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="20"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
@@ -10993,12 +10993,12 @@
       <c r="E8" s="4">
         <v>0.11</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
@@ -11016,12 +11016,12 @@
       <c r="E9" s="4">
         <v>0.18</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="20"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
@@ -11039,15 +11039,15 @@
       <c r="E10" s="4">
         <v>0.13</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="20"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>536</v>
       </c>
       <c r="B13" s="13"/>
@@ -11108,7 +11108,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>549</v>
       </c>
       <c r="B22" s="13"/>
@@ -11150,10 +11150,10 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="20" t="s">
         <v>530</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="20" t="s">
         <v>558</v>
       </c>
       <c r="C24" s="4">
@@ -11179,8 +11179,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
       <c r="C25" s="4">
         <v>1</v>
       </c>
@@ -11204,8 +11204,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="4">
         <v>2</v>
       </c>
@@ -11229,8 +11229,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="4">
         <v>3</v>
       </c>
@@ -11254,8 +11254,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="4">
         <v>4</v>
       </c>
@@ -11279,8 +11279,8 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
       <c r="C29" s="4">
         <v>5</v>
       </c>
@@ -11304,8 +11304,8 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="4">
         <v>6</v>
       </c>
@@ -11329,8 +11329,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
       <c r="C31" s="4">
         <v>7</v>
       </c>
@@ -11354,8 +11354,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="4">
         <v>8</v>
       </c>
@@ -11379,8 +11379,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="26"/>
       <c r="C33" s="4">
         <v>9</v>
       </c>
@@ -11404,8 +11404,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
       <c r="C34" s="4">
         <v>10</v>
       </c>
@@ -11429,10 +11429,10 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="20" t="s">
         <v>559</v>
       </c>
       <c r="C35" s="4">
@@ -11458,8 +11458,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25"/>
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="4">
         <v>1</v>
       </c>
@@ -11483,8 +11483,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
       <c r="C37" s="4">
         <v>2</v>
       </c>
@@ -11508,8 +11508,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="26"/>
       <c r="C38" s="4">
         <v>3</v>
       </c>
@@ -11533,8 +11533,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="26"/>
       <c r="C39" s="4">
         <v>4</v>
       </c>
@@ -11558,8 +11558,8 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" s="25"/>
-      <c r="B40" s="25"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="26"/>
       <c r="C40" s="4">
         <v>5</v>
       </c>
@@ -11583,8 +11583,8 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" s="25"/>
-      <c r="B41" s="25"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="26"/>
       <c r="C41" s="4">
         <v>6</v>
       </c>
@@ -11608,8 +11608,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="25"/>
-      <c r="B42" s="25"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="26"/>
       <c r="C42" s="4">
         <v>7</v>
       </c>
@@ -11633,8 +11633,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
       <c r="C43" s="4">
         <v>8</v>
       </c>
@@ -11658,8 +11658,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
       <c r="C44" s="4">
         <v>9</v>
       </c>
@@ -11683,8 +11683,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
       <c r="C45" s="4">
         <v>10</v>
       </c>
@@ -11708,10 +11708,10 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="20" t="s">
         <v>532</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="20" t="s">
         <v>560</v>
       </c>
       <c r="C46" s="4">
@@ -11737,8 +11737,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="25"/>
-      <c r="B47" s="25"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
       <c r="C47" s="4">
         <v>1</v>
       </c>
@@ -11762,8 +11762,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="25"/>
-      <c r="B48" s="25"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
       <c r="C48" s="4">
         <v>2</v>
       </c>
@@ -11787,8 +11787,8 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
+      <c r="A49" s="26"/>
+      <c r="B49" s="26"/>
       <c r="C49" s="4">
         <v>3</v>
       </c>
@@ -11812,8 +11812,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="25"/>
-      <c r="B50" s="25"/>
+      <c r="A50" s="26"/>
+      <c r="B50" s="26"/>
       <c r="C50" s="4">
         <v>4</v>
       </c>
@@ -11837,8 +11837,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" s="25"/>
-      <c r="B51" s="25"/>
+      <c r="A51" s="26"/>
+      <c r="B51" s="26"/>
       <c r="C51" s="4">
         <v>5</v>
       </c>
@@ -11862,8 +11862,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="25"/>
-      <c r="B52" s="25"/>
+      <c r="A52" s="26"/>
+      <c r="B52" s="26"/>
       <c r="C52" s="4">
         <v>6</v>
       </c>
@@ -11887,8 +11887,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53" s="25"/>
-      <c r="B53" s="25"/>
+      <c r="A53" s="26"/>
+      <c r="B53" s="26"/>
       <c r="C53" s="4">
         <v>7</v>
       </c>
@@ -11912,8 +11912,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="25"/>
-      <c r="B54" s="25"/>
+      <c r="A54" s="26"/>
+      <c r="B54" s="26"/>
       <c r="C54" s="4">
         <v>8</v>
       </c>
@@ -11937,8 +11937,8 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55" s="25"/>
-      <c r="B55" s="25"/>
+      <c r="A55" s="26"/>
+      <c r="B55" s="26"/>
       <c r="C55" s="4">
         <v>9</v>
       </c>
@@ -11962,8 +11962,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" s="24"/>
-      <c r="B56" s="24"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
       <c r="C56" s="4">
         <v>10</v>
       </c>
@@ -11987,10 +11987,10 @@
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="20" t="s">
         <v>533</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="20" t="s">
         <v>561</v>
       </c>
       <c r="C57" s="4">
@@ -12016,8 +12016,8 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" s="25"/>
-      <c r="B58" s="25"/>
+      <c r="A58" s="26"/>
+      <c r="B58" s="26"/>
       <c r="C58" s="4">
         <v>1</v>
       </c>
@@ -12041,8 +12041,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59" s="25"/>
-      <c r="B59" s="25"/>
+      <c r="A59" s="26"/>
+      <c r="B59" s="26"/>
       <c r="C59" s="4">
         <v>2</v>
       </c>
@@ -12066,8 +12066,8 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" s="25"/>
-      <c r="B60" s="25"/>
+      <c r="A60" s="26"/>
+      <c r="B60" s="26"/>
       <c r="C60" s="4">
         <v>3</v>
       </c>
@@ -12091,8 +12091,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A61" s="25"/>
-      <c r="B61" s="25"/>
+      <c r="A61" s="26"/>
+      <c r="B61" s="26"/>
       <c r="C61" s="4">
         <v>4</v>
       </c>
@@ -12116,8 +12116,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A62" s="25"/>
-      <c r="B62" s="25"/>
+      <c r="A62" s="26"/>
+      <c r="B62" s="26"/>
       <c r="C62" s="4">
         <v>5</v>
       </c>
@@ -12141,8 +12141,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" s="25"/>
-      <c r="B63" s="25"/>
+      <c r="A63" s="26"/>
+      <c r="B63" s="26"/>
       <c r="C63" s="4">
         <v>6</v>
       </c>
@@ -12166,8 +12166,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
+      <c r="A64" s="26"/>
+      <c r="B64" s="26"/>
       <c r="C64" s="4">
         <v>7</v>
       </c>
@@ -12191,8 +12191,8 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" s="25"/>
-      <c r="B65" s="25"/>
+      <c r="A65" s="26"/>
+      <c r="B65" s="26"/>
       <c r="C65" s="4">
         <v>8</v>
       </c>
@@ -12216,8 +12216,8 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" s="25"/>
-      <c r="B66" s="25"/>
+      <c r="A66" s="26"/>
+      <c r="B66" s="26"/>
       <c r="C66" s="4">
         <v>9</v>
       </c>
@@ -12241,8 +12241,8 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" s="24"/>
-      <c r="B67" s="24"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="23"/>
       <c r="C67" s="4">
         <v>10</v>
       </c>
@@ -12266,10 +12266,10 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="20" t="s">
         <v>534</v>
       </c>
-      <c r="B68" s="21" t="s">
+      <c r="B68" s="20" t="s">
         <v>562</v>
       </c>
       <c r="C68" s="4">
@@ -12295,8 +12295,8 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="25"/>
-      <c r="B69" s="25"/>
+      <c r="A69" s="26"/>
+      <c r="B69" s="26"/>
       <c r="C69" s="4">
         <v>1</v>
       </c>
@@ -12320,8 +12320,8 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" s="25"/>
-      <c r="B70" s="25"/>
+      <c r="A70" s="26"/>
+      <c r="B70" s="26"/>
       <c r="C70" s="4">
         <v>2</v>
       </c>
@@ -12345,8 +12345,8 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="25"/>
-      <c r="B71" s="25"/>
+      <c r="A71" s="26"/>
+      <c r="B71" s="26"/>
       <c r="C71" s="4">
         <v>3</v>
       </c>
@@ -12370,8 +12370,8 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="25"/>
-      <c r="B72" s="25"/>
+      <c r="A72" s="26"/>
+      <c r="B72" s="26"/>
       <c r="C72" s="4">
         <v>4</v>
       </c>
@@ -12395,8 +12395,8 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" s="25"/>
-      <c r="B73" s="25"/>
+      <c r="A73" s="26"/>
+      <c r="B73" s="26"/>
       <c r="C73" s="4">
         <v>5</v>
       </c>
@@ -12420,8 +12420,8 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A74" s="25"/>
-      <c r="B74" s="25"/>
+      <c r="A74" s="26"/>
+      <c r="B74" s="26"/>
       <c r="C74" s="4">
         <v>6</v>
       </c>
@@ -12445,8 +12445,8 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="25"/>
-      <c r="B75" s="25"/>
+      <c r="A75" s="26"/>
+      <c r="B75" s="26"/>
       <c r="C75" s="4">
         <v>7</v>
       </c>
@@ -12470,8 +12470,8 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" s="25"/>
-      <c r="B76" s="25"/>
+      <c r="A76" s="26"/>
+      <c r="B76" s="26"/>
       <c r="C76" s="4">
         <v>8</v>
       </c>
@@ -12495,8 +12495,8 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A77" s="25"/>
-      <c r="B77" s="25"/>
+      <c r="A77" s="26"/>
+      <c r="B77" s="26"/>
       <c r="C77" s="4">
         <v>9</v>
       </c>
@@ -12520,8 +12520,8 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A78" s="24"/>
-      <c r="B78" s="24"/>
+      <c r="A78" s="23"/>
+      <c r="B78" s="23"/>
       <c r="C78" s="4">
         <v>10</v>
       </c>
@@ -12545,10 +12545,10 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A79" s="21" t="s">
+      <c r="A79" s="20" t="s">
         <v>535</v>
       </c>
-      <c r="B79" s="21" t="s">
+      <c r="B79" s="20" t="s">
         <v>563</v>
       </c>
       <c r="C79" s="4">
@@ -12574,8 +12574,8 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" s="25"/>
-      <c r="B80" s="25"/>
+      <c r="A80" s="26"/>
+      <c r="B80" s="26"/>
       <c r="C80" s="4">
         <v>1</v>
       </c>
@@ -12599,8 +12599,8 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A81" s="25"/>
-      <c r="B81" s="25"/>
+      <c r="A81" s="26"/>
+      <c r="B81" s="26"/>
       <c r="C81" s="4">
         <v>2</v>
       </c>
@@ -12624,8 +12624,8 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A82" s="25"/>
-      <c r="B82" s="25"/>
+      <c r="A82" s="26"/>
+      <c r="B82" s="26"/>
       <c r="C82" s="4">
         <v>3</v>
       </c>
@@ -12649,8 +12649,8 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A83" s="25"/>
-      <c r="B83" s="25"/>
+      <c r="A83" s="26"/>
+      <c r="B83" s="26"/>
       <c r="C83" s="4">
         <v>4</v>
       </c>
@@ -12674,8 +12674,8 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A84" s="25"/>
-      <c r="B84" s="25"/>
+      <c r="A84" s="26"/>
+      <c r="B84" s="26"/>
       <c r="C84" s="4">
         <v>5</v>
       </c>
@@ -12699,8 +12699,8 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A85" s="25"/>
-      <c r="B85" s="25"/>
+      <c r="A85" s="26"/>
+      <c r="B85" s="26"/>
       <c r="C85" s="4">
         <v>6</v>
       </c>
@@ -12724,8 +12724,8 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A86" s="25"/>
-      <c r="B86" s="25"/>
+      <c r="A86" s="26"/>
+      <c r="B86" s="26"/>
       <c r="C86" s="4">
         <v>7</v>
       </c>
@@ -12749,8 +12749,8 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A87" s="25"/>
-      <c r="B87" s="25"/>
+      <c r="A87" s="26"/>
+      <c r="B87" s="26"/>
       <c r="C87" s="4">
         <v>8</v>
       </c>
@@ -12774,8 +12774,8 @@
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A88" s="25"/>
-      <c r="B88" s="25"/>
+      <c r="A88" s="26"/>
+      <c r="B88" s="26"/>
       <c r="C88" s="4">
         <v>9</v>
       </c>
@@ -12799,8 +12799,8 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A89" s="24"/>
-      <c r="B89" s="24"/>
+      <c r="A89" s="23"/>
+      <c r="B89" s="23"/>
       <c r="C89" s="4">
         <v>10</v>
       </c>
@@ -12824,7 +12824,7 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A91" s="17" t="s">
+      <c r="A91" s="14" t="s">
         <v>311</v>
       </c>
       <c r="B91" s="13"/>
@@ -12837,7 +12837,7 @@
       <c r="I91" s="13"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A92" s="26" t="s">
+      <c r="A92" s="15" t="s">
         <v>564</v>
       </c>
       <c r="B92" s="13"/>
@@ -12850,7 +12850,7 @@
       <c r="I92" s="13"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A93" s="26" t="s">
+      <c r="A93" s="15" t="s">
         <v>565</v>
       </c>
       <c r="B93" s="13"/>
@@ -12863,7 +12863,7 @@
       <c r="I93" s="13"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A94" s="26" t="s">
+      <c r="A94" s="15" t="s">
         <v>566</v>
       </c>
       <c r="B94" s="13"/>
@@ -12876,7 +12876,7 @@
       <c r="I94" s="13"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A95" s="26" t="s">
+      <c r="A95" s="15" t="s">
         <v>567</v>
       </c>
       <c r="B95" s="13"/>
@@ -12889,7 +12889,7 @@
       <c r="I95" s="13"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A96" s="26" t="s">
+      <c r="A96" s="15" t="s">
         <v>568</v>
       </c>
       <c r="B96" s="13"/>
@@ -12902,7 +12902,7 @@
       <c r="I96" s="13"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="24" t="s">
         <v>569</v>
       </c>
       <c r="B99" s="13"/>
@@ -12937,10 +12937,10 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="21" t="s">
+      <c r="A101" s="20" t="s">
         <v>530</v>
       </c>
-      <c r="B101" s="21" t="s">
+      <c r="B101" s="20" t="s">
         <v>558</v>
       </c>
       <c r="C101" s="4">
@@ -12960,8 +12960,8 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="25"/>
-      <c r="B102" s="25"/>
+      <c r="A102" s="26"/>
+      <c r="B102" s="26"/>
       <c r="C102" s="4">
         <v>1</v>
       </c>
@@ -12979,8 +12979,8 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="25"/>
-      <c r="B103" s="25"/>
+      <c r="A103" s="26"/>
+      <c r="B103" s="26"/>
       <c r="C103" s="4">
         <v>2</v>
       </c>
@@ -12998,8 +12998,8 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="25"/>
-      <c r="B104" s="25"/>
+      <c r="A104" s="26"/>
+      <c r="B104" s="26"/>
       <c r="C104" s="4">
         <v>3</v>
       </c>
@@ -13017,8 +13017,8 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" s="25"/>
-      <c r="B105" s="25"/>
+      <c r="A105" s="26"/>
+      <c r="B105" s="26"/>
       <c r="C105" s="4">
         <v>4</v>
       </c>
@@ -13036,8 +13036,8 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="25"/>
-      <c r="B106" s="25"/>
+      <c r="A106" s="26"/>
+      <c r="B106" s="26"/>
       <c r="C106" s="4">
         <v>5</v>
       </c>
@@ -13055,8 +13055,8 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" s="25"/>
-      <c r="B107" s="25"/>
+      <c r="A107" s="26"/>
+      <c r="B107" s="26"/>
       <c r="C107" s="4">
         <v>6</v>
       </c>
@@ -13074,8 +13074,8 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="25"/>
-      <c r="B108" s="25"/>
+      <c r="A108" s="26"/>
+      <c r="B108" s="26"/>
       <c r="C108" s="4">
         <v>7</v>
       </c>
@@ -13093,8 +13093,8 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="25"/>
-      <c r="B109" s="25"/>
+      <c r="A109" s="26"/>
+      <c r="B109" s="26"/>
       <c r="C109" s="4">
         <v>8</v>
       </c>
@@ -13112,8 +13112,8 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" s="25"/>
-      <c r="B110" s="25"/>
+      <c r="A110" s="26"/>
+      <c r="B110" s="26"/>
       <c r="C110" s="4">
         <v>9</v>
       </c>
@@ -13131,8 +13131,8 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" s="24"/>
-      <c r="B111" s="24"/>
+      <c r="A111" s="23"/>
+      <c r="B111" s="23"/>
       <c r="C111" s="4">
         <v>10</v>
       </c>
@@ -13150,10 +13150,10 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" s="21" t="s">
+      <c r="A112" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="B112" s="21" t="s">
+      <c r="B112" s="20" t="s">
         <v>559</v>
       </c>
       <c r="C112" s="4">
@@ -13173,8 +13173,8 @@
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" s="25"/>
-      <c r="B113" s="25"/>
+      <c r="A113" s="26"/>
+      <c r="B113" s="26"/>
       <c r="C113" s="4">
         <v>1</v>
       </c>
@@ -13192,8 +13192,8 @@
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" s="25"/>
-      <c r="B114" s="25"/>
+      <c r="A114" s="26"/>
+      <c r="B114" s="26"/>
       <c r="C114" s="4">
         <v>2</v>
       </c>
@@ -13211,8 +13211,8 @@
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" s="25"/>
-      <c r="B115" s="25"/>
+      <c r="A115" s="26"/>
+      <c r="B115" s="26"/>
       <c r="C115" s="4">
         <v>3</v>
       </c>
@@ -13230,8 +13230,8 @@
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" s="25"/>
-      <c r="B116" s="25"/>
+      <c r="A116" s="26"/>
+      <c r="B116" s="26"/>
       <c r="C116" s="4">
         <v>4</v>
       </c>
@@ -13249,8 +13249,8 @@
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" s="25"/>
-      <c r="B117" s="25"/>
+      <c r="A117" s="26"/>
+      <c r="B117" s="26"/>
       <c r="C117" s="4">
         <v>5</v>
       </c>
@@ -13268,8 +13268,8 @@
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" s="25"/>
-      <c r="B118" s="25"/>
+      <c r="A118" s="26"/>
+      <c r="B118" s="26"/>
       <c r="C118" s="4">
         <v>6</v>
       </c>
@@ -13287,8 +13287,8 @@
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" s="25"/>
-      <c r="B119" s="25"/>
+      <c r="A119" s="26"/>
+      <c r="B119" s="26"/>
       <c r="C119" s="4">
         <v>7</v>
       </c>
@@ -13306,8 +13306,8 @@
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="25"/>
-      <c r="B120" s="25"/>
+      <c r="A120" s="26"/>
+      <c r="B120" s="26"/>
       <c r="C120" s="4">
         <v>8</v>
       </c>
@@ -13325,8 +13325,8 @@
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121" s="25"/>
-      <c r="B121" s="25"/>
+      <c r="A121" s="26"/>
+      <c r="B121" s="26"/>
       <c r="C121" s="4">
         <v>9</v>
       </c>
@@ -13344,8 +13344,8 @@
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" s="24"/>
-      <c r="B122" s="24"/>
+      <c r="A122" s="23"/>
+      <c r="B122" s="23"/>
       <c r="C122" s="4">
         <v>10</v>
       </c>
@@ -13363,10 +13363,10 @@
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="21" t="s">
+      <c r="A123" s="20" t="s">
         <v>532</v>
       </c>
-      <c r="B123" s="21" t="s">
+      <c r="B123" s="20" t="s">
         <v>560</v>
       </c>
       <c r="C123" s="4">
@@ -13386,8 +13386,8 @@
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="25"/>
-      <c r="B124" s="25"/>
+      <c r="A124" s="26"/>
+      <c r="B124" s="26"/>
       <c r="C124" s="4">
         <v>1</v>
       </c>
@@ -13405,8 +13405,8 @@
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" s="25"/>
-      <c r="B125" s="25"/>
+      <c r="A125" s="26"/>
+      <c r="B125" s="26"/>
       <c r="C125" s="4">
         <v>2</v>
       </c>
@@ -13424,8 +13424,8 @@
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" s="25"/>
-      <c r="B126" s="25"/>
+      <c r="A126" s="26"/>
+      <c r="B126" s="26"/>
       <c r="C126" s="4">
         <v>3</v>
       </c>
@@ -13443,8 +13443,8 @@
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127" s="25"/>
-      <c r="B127" s="25"/>
+      <c r="A127" s="26"/>
+      <c r="B127" s="26"/>
       <c r="C127" s="4">
         <v>4</v>
       </c>
@@ -13462,8 +13462,8 @@
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128" s="25"/>
-      <c r="B128" s="25"/>
+      <c r="A128" s="26"/>
+      <c r="B128" s="26"/>
       <c r="C128" s="4">
         <v>5</v>
       </c>
@@ -13481,8 +13481,8 @@
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A129" s="25"/>
-      <c r="B129" s="25"/>
+      <c r="A129" s="26"/>
+      <c r="B129" s="26"/>
       <c r="C129" s="4">
         <v>6</v>
       </c>
@@ -13500,8 +13500,8 @@
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130" s="25"/>
-      <c r="B130" s="25"/>
+      <c r="A130" s="26"/>
+      <c r="B130" s="26"/>
       <c r="C130" s="4">
         <v>7</v>
       </c>
@@ -13519,8 +13519,8 @@
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" s="25"/>
-      <c r="B131" s="25"/>
+      <c r="A131" s="26"/>
+      <c r="B131" s="26"/>
       <c r="C131" s="4">
         <v>8</v>
       </c>
@@ -13538,8 +13538,8 @@
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132" s="25"/>
-      <c r="B132" s="25"/>
+      <c r="A132" s="26"/>
+      <c r="B132" s="26"/>
       <c r="C132" s="4">
         <v>9</v>
       </c>
@@ -13557,8 +13557,8 @@
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A133" s="24"/>
-      <c r="B133" s="24"/>
+      <c r="A133" s="23"/>
+      <c r="B133" s="23"/>
       <c r="C133" s="4">
         <v>10</v>
       </c>
@@ -13576,10 +13576,10 @@
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A134" s="21" t="s">
+      <c r="A134" s="20" t="s">
         <v>533</v>
       </c>
-      <c r="B134" s="21" t="s">
+      <c r="B134" s="20" t="s">
         <v>561</v>
       </c>
       <c r="C134" s="4">
@@ -13599,8 +13599,8 @@
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A135" s="25"/>
-      <c r="B135" s="25"/>
+      <c r="A135" s="26"/>
+      <c r="B135" s="26"/>
       <c r="C135" s="4">
         <v>1</v>
       </c>
@@ -13618,8 +13618,8 @@
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A136" s="25"/>
-      <c r="B136" s="25"/>
+      <c r="A136" s="26"/>
+      <c r="B136" s="26"/>
       <c r="C136" s="4">
         <v>2</v>
       </c>
@@ -13637,8 +13637,8 @@
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137" s="25"/>
-      <c r="B137" s="25"/>
+      <c r="A137" s="26"/>
+      <c r="B137" s="26"/>
       <c r="C137" s="4">
         <v>3</v>
       </c>
@@ -13656,8 +13656,8 @@
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A138" s="25"/>
-      <c r="B138" s="25"/>
+      <c r="A138" s="26"/>
+      <c r="B138" s="26"/>
       <c r="C138" s="4">
         <v>4</v>
       </c>
@@ -13675,8 +13675,8 @@
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A139" s="25"/>
-      <c r="B139" s="25"/>
+      <c r="A139" s="26"/>
+      <c r="B139" s="26"/>
       <c r="C139" s="4">
         <v>5</v>
       </c>
@@ -13694,8 +13694,8 @@
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140" s="25"/>
-      <c r="B140" s="25"/>
+      <c r="A140" s="26"/>
+      <c r="B140" s="26"/>
       <c r="C140" s="4">
         <v>6</v>
       </c>
@@ -13713,8 +13713,8 @@
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141" s="25"/>
-      <c r="B141" s="25"/>
+      <c r="A141" s="26"/>
+      <c r="B141" s="26"/>
       <c r="C141" s="4">
         <v>7</v>
       </c>
@@ -13732,8 +13732,8 @@
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A142" s="25"/>
-      <c r="B142" s="25"/>
+      <c r="A142" s="26"/>
+      <c r="B142" s="26"/>
       <c r="C142" s="4">
         <v>8</v>
       </c>
@@ -13751,8 +13751,8 @@
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A143" s="25"/>
-      <c r="B143" s="25"/>
+      <c r="A143" s="26"/>
+      <c r="B143" s="26"/>
       <c r="C143" s="4">
         <v>9</v>
       </c>
@@ -13770,8 +13770,8 @@
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A144" s="24"/>
-      <c r="B144" s="24"/>
+      <c r="A144" s="23"/>
+      <c r="B144" s="23"/>
       <c r="C144" s="4">
         <v>10</v>
       </c>
@@ -13789,10 +13789,10 @@
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A145" s="21" t="s">
+      <c r="A145" s="20" t="s">
         <v>534</v>
       </c>
-      <c r="B145" s="21" t="s">
+      <c r="B145" s="20" t="s">
         <v>562</v>
       </c>
       <c r="C145" s="4">
@@ -13812,8 +13812,8 @@
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A146" s="25"/>
-      <c r="B146" s="25"/>
+      <c r="A146" s="26"/>
+      <c r="B146" s="26"/>
       <c r="C146" s="4">
         <v>1</v>
       </c>
@@ -13831,8 +13831,8 @@
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A147" s="25"/>
-      <c r="B147" s="25"/>
+      <c r="A147" s="26"/>
+      <c r="B147" s="26"/>
       <c r="C147" s="4">
         <v>2</v>
       </c>
@@ -13850,8 +13850,8 @@
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A148" s="25"/>
-      <c r="B148" s="25"/>
+      <c r="A148" s="26"/>
+      <c r="B148" s="26"/>
       <c r="C148" s="4">
         <v>3</v>
       </c>
@@ -13869,8 +13869,8 @@
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A149" s="25"/>
-      <c r="B149" s="25"/>
+      <c r="A149" s="26"/>
+      <c r="B149" s="26"/>
       <c r="C149" s="4">
         <v>4</v>
       </c>
@@ -13888,8 +13888,8 @@
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A150" s="25"/>
-      <c r="B150" s="25"/>
+      <c r="A150" s="26"/>
+      <c r="B150" s="26"/>
       <c r="C150" s="4">
         <v>5</v>
       </c>
@@ -13907,8 +13907,8 @@
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A151" s="25"/>
-      <c r="B151" s="25"/>
+      <c r="A151" s="26"/>
+      <c r="B151" s="26"/>
       <c r="C151" s="4">
         <v>6</v>
       </c>
@@ -13926,8 +13926,8 @@
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A152" s="25"/>
-      <c r="B152" s="25"/>
+      <c r="A152" s="26"/>
+      <c r="B152" s="26"/>
       <c r="C152" s="4">
         <v>7</v>
       </c>
@@ -13945,8 +13945,8 @@
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A153" s="25"/>
-      <c r="B153" s="25"/>
+      <c r="A153" s="26"/>
+      <c r="B153" s="26"/>
       <c r="C153" s="4">
         <v>8</v>
       </c>
@@ -13964,8 +13964,8 @@
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A154" s="25"/>
-      <c r="B154" s="25"/>
+      <c r="A154" s="26"/>
+      <c r="B154" s="26"/>
       <c r="C154" s="4">
         <v>9</v>
       </c>
@@ -13983,8 +13983,8 @@
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A155" s="24"/>
-      <c r="B155" s="24"/>
+      <c r="A155" s="23"/>
+      <c r="B155" s="23"/>
       <c r="C155" s="4">
         <v>10</v>
       </c>
@@ -14002,10 +14002,10 @@
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="20" t="s">
         <v>535</v>
       </c>
-      <c r="B156" s="21" t="s">
+      <c r="B156" s="20" t="s">
         <v>563</v>
       </c>
       <c r="C156" s="4">
@@ -14025,8 +14025,8 @@
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A157" s="25"/>
-      <c r="B157" s="25"/>
+      <c r="A157" s="26"/>
+      <c r="B157" s="26"/>
       <c r="C157" s="4">
         <v>1</v>
       </c>
@@ -14044,8 +14044,8 @@
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A158" s="25"/>
-      <c r="B158" s="25"/>
+      <c r="A158" s="26"/>
+      <c r="B158" s="26"/>
       <c r="C158" s="4">
         <v>2</v>
       </c>
@@ -14063,8 +14063,8 @@
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A159" s="25"/>
-      <c r="B159" s="25"/>
+      <c r="A159" s="26"/>
+      <c r="B159" s="26"/>
       <c r="C159" s="4">
         <v>3</v>
       </c>
@@ -14082,8 +14082,8 @@
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A160" s="25"/>
-      <c r="B160" s="25"/>
+      <c r="A160" s="26"/>
+      <c r="B160" s="26"/>
       <c r="C160" s="4">
         <v>4</v>
       </c>
@@ -14101,8 +14101,8 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A161" s="25"/>
-      <c r="B161" s="25"/>
+      <c r="A161" s="26"/>
+      <c r="B161" s="26"/>
       <c r="C161" s="4">
         <v>5</v>
       </c>
@@ -14120,8 +14120,8 @@
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A162" s="25"/>
-      <c r="B162" s="25"/>
+      <c r="A162" s="26"/>
+      <c r="B162" s="26"/>
       <c r="C162" s="4">
         <v>6</v>
       </c>
@@ -14139,8 +14139,8 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A163" s="25"/>
-      <c r="B163" s="25"/>
+      <c r="A163" s="26"/>
+      <c r="B163" s="26"/>
       <c r="C163" s="4">
         <v>7</v>
       </c>
@@ -14158,8 +14158,8 @@
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A164" s="25"/>
-      <c r="B164" s="25"/>
+      <c r="A164" s="26"/>
+      <c r="B164" s="26"/>
       <c r="C164" s="4">
         <v>8</v>
       </c>
@@ -14177,8 +14177,8 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A165" s="25"/>
-      <c r="B165" s="25"/>
+      <c r="A165" s="26"/>
+      <c r="B165" s="26"/>
       <c r="C165" s="4">
         <v>9</v>
       </c>
@@ -14196,8 +14196,8 @@
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A166" s="24"/>
-      <c r="B166" s="24"/>
+      <c r="A166" s="23"/>
+      <c r="B166" s="23"/>
       <c r="C166" s="4">
         <v>10</v>
       </c>
@@ -14215,7 +14215,7 @@
       </c>
     </row>
     <row r="168" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="14" t="s">
+      <c r="A168" s="25" t="s">
         <v>574</v>
       </c>
       <c r="B168" s="13"/>
@@ -14228,6 +14228,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B145:B155"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B101:B111"/>
+    <mergeCell ref="A168:H168"/>
+    <mergeCell ref="B57:B67"/>
+    <mergeCell ref="A95:I95"/>
+    <mergeCell ref="A145:A155"/>
+    <mergeCell ref="A101:A111"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="A46:A56"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="B112:B122"/>
+    <mergeCell ref="B68:B78"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A91:I91"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A112:A122"/>
+    <mergeCell ref="B24:B34"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="A96:I96"/>
+    <mergeCell ref="A57:A67"/>
+    <mergeCell ref="B123:B133"/>
+    <mergeCell ref="A68:A78"/>
+    <mergeCell ref="A123:A133"/>
+    <mergeCell ref="B134:B144"/>
+    <mergeCell ref="A134:A144"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A94:I94"/>
     <mergeCell ref="B156:B166"/>
@@ -14244,33 +14271,6 @@
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="A93:I93"/>
     <mergeCell ref="A13:I13"/>
-    <mergeCell ref="B123:B133"/>
-    <mergeCell ref="A68:A78"/>
-    <mergeCell ref="A123:A133"/>
-    <mergeCell ref="B134:B144"/>
-    <mergeCell ref="A134:A144"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A112:A122"/>
-    <mergeCell ref="B24:B34"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="A96:I96"/>
-    <mergeCell ref="A57:A67"/>
-    <mergeCell ref="B145:B155"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="B101:B111"/>
-    <mergeCell ref="A168:H168"/>
-    <mergeCell ref="B57:B67"/>
-    <mergeCell ref="A95:I95"/>
-    <mergeCell ref="A145:A155"/>
-    <mergeCell ref="A101:A111"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A46:A56"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="B112:B122"/>
-    <mergeCell ref="B68:B78"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A91:I91"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14300,7 +14300,7 @@
       <c r="I1" s="13"/>
     </row>
     <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>576</v>
       </c>
       <c r="B3" s="13"/>
@@ -14458,7 +14458,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>587</v>
       </c>
       <c r="B11" s="13"/>
@@ -14641,7 +14641,7 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="14" t="s">
         <v>311</v>
       </c>
       <c r="B23" s="13"/>
@@ -14654,7 +14654,7 @@
       <c r="I23" s="13"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="15" t="s">
         <v>593</v>
       </c>
       <c r="B24" s="13"/>
@@ -14667,7 +14667,7 @@
       <c r="I24" s="13"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="15" t="s">
         <v>594</v>
       </c>
       <c r="B25" s="13"/>
@@ -14680,7 +14680,7 @@
       <c r="I25" s="13"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="15" t="s">
         <v>595</v>
       </c>
       <c r="B26" s="13"/>
@@ -14693,7 +14693,7 @@
       <c r="I26" s="13"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="15" t="s">
         <v>596</v>
       </c>
       <c r="B27" s="13"/>
@@ -14706,7 +14706,7 @@
       <c r="I27" s="13"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="15" t="s">
         <v>597</v>
       </c>
       <c r="B28" s="13"/>
@@ -14719,7 +14719,7 @@
       <c r="I28" s="13"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="15" t="s">
         <v>598</v>
       </c>
       <c r="B29" s="13"/>
@@ -14732,7 +14732,7 @@
       <c r="I29" s="13"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="15" t="s">
         <v>599</v>
       </c>
       <c r="B30" s="13"/>
@@ -14785,7 +14785,7 @@
       <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>601</v>
       </c>
       <c r="B3" s="13"/>
@@ -14798,76 +14798,76 @@
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="21" t="s">
         <v>602</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>604</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>606</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>608</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>610</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>540</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>612</v>
       </c>
       <c r="B12" s="13"/>
@@ -14957,7 +14957,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>617</v>
       </c>
       <c r="B19" s="13"/>
@@ -15127,7 +15127,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="14" t="s">
         <v>311</v>
       </c>
       <c r="B29" s="13"/>
@@ -15137,7 +15137,7 @@
       <c r="F29" s="13"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="15" t="s">
         <v>634</v>
       </c>
       <c r="B30" s="13"/>
@@ -15147,7 +15147,7 @@
       <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="15" t="s">
         <v>635</v>
       </c>
       <c r="B31" s="13"/>
@@ -15157,7 +15157,7 @@
       <c r="F31" s="13"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="15" t="s">
         <v>636</v>
       </c>
       <c r="B32" s="13"/>
@@ -15167,7 +15167,7 @@
       <c r="F32" s="13"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="15" t="s">
         <v>637</v>
       </c>
       <c r="B33" s="13"/>
@@ -15177,7 +15177,7 @@
       <c r="F33" s="13"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="15" t="s">
         <v>638</v>
       </c>
       <c r="B34" s="13"/>
@@ -15187,7 +15187,7 @@
       <c r="F34" s="13"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="15" t="s">
         <v>639</v>
       </c>
       <c r="B35" s="13"/>
@@ -15197,7 +15197,7 @@
       <c r="F35" s="13"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="15" t="s">
         <v>640</v>
       </c>
       <c r="B36" s="13"/>
@@ -15208,13 +15208,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="B5:F5"/>
@@ -15226,6 +15219,13 @@
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
